--- a/TestData/TMTT0035667_VerifyInternalDealTeamForAnalystRoleLimitForFVALOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035667_VerifyInternalDealTeamForAnalystRoleLimitForFVALOBOpportunityEngagement.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4AED04-15D2-4324-85E9-F896EF547778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6063D0B1-095F-41C5-BF99-FF27D057A0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28950" windowHeight="14610" firstSheet="1" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="139">
   <si>
     <t>Client</t>
   </si>
@@ -293,9 +293,6 @@
     <t>Preston Wolf</t>
   </si>
   <si>
-    <t>Rich Bowman</t>
-  </si>
-  <si>
     <t>Rittik Chakrabarti</t>
   </si>
   <si>
@@ -395,19 +392,10 @@
     <t>Akshat Jamad</t>
   </si>
   <si>
-    <t>Alan Frederick Hall</t>
-  </si>
-  <si>
     <t>Alberico Altieri</t>
   </si>
   <si>
-    <t>Alberto Alonso Basagoiti</t>
-  </si>
-  <si>
     <t>Albert Sung</t>
-  </si>
-  <si>
-    <t>Alejandro Arturo Serrano Leo</t>
   </si>
   <si>
     <t>Aleksandra Chadam</t>
@@ -529,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -543,7 +531,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -859,12 +846,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -953,7 +940,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1050,9 +1037,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1047,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1076,9 +1063,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -1104,7 +1091,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -1138,318 +1125,315 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>77</v>
       </c>
-      <c r="D13" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1460,37 +1444,37 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B2">
         <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I2">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B3">
         <v>65</v>
@@ -1504,24 +1488,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1532,34 +1516,34 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="76.21875" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="76.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="B2" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0035667_VerifyInternalDealTeamForAnalystRoleLimitForFVALOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035667_VerifyInternalDealTeamForAnalystRoleLimitForFVALOBOpportunityEngagement.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6063D0B1-095F-41C5-BF99-FF27D057A0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B04F765-3300-4DB3-8110-E75D331EFFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28950" windowHeight="14610" firstSheet="1" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
-    <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="AddContact" sheetId="3" r:id="rId3"/>
-    <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId4"/>
-    <sheet name="Roles" sheetId="7" r:id="rId5"/>
-    <sheet name="EngDealTeamMembers" sheetId="5" r:id="rId6"/>
-    <sheet name="OverlimitMessage" sheetId="6" r:id="rId7"/>
+    <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
+    <sheet name="CAOUser" sheetId="8" r:id="rId2"/>
+    <sheet name="AppName" sheetId="9" r:id="rId3"/>
+    <sheet name="ModuleName" sheetId="10" r:id="rId4"/>
+    <sheet name="AddOpportunity" sheetId="1" r:id="rId5"/>
+    <sheet name="AddContact" sheetId="3" r:id="rId6"/>
+    <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId7"/>
+    <sheet name="EngDealTeamMembers" sheetId="5" r:id="rId8"/>
+    <sheet name="Roles" sheetId="7" r:id="rId9"/>
+    <sheet name="OverlimitMessage" sheetId="6" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="145">
   <si>
     <t>Client</t>
   </si>
@@ -134,12 +137,6 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>FA - Portfolio-Advis/Consulting</t>
-  </si>
-  <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -158,9 +155,6 @@
     <t>Do Not Disclose</t>
   </si>
   <si>
-    <t>Drew Koecher</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -194,15 +188,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>StdUser</t>
-  </si>
-  <si>
-    <t>CaoUser</t>
-  </si>
-  <si>
-    <t>Danielle Morello</t>
-  </si>
-  <si>
     <t>Contact</t>
   </si>
   <si>
@@ -260,18 +245,12 @@
     <t>Dimitri Drone</t>
   </si>
   <si>
-    <t>Jason Vierig</t>
-  </si>
-  <si>
     <t>Karim Jooma</t>
   </si>
   <si>
     <t>Kyle Poorman</t>
   </si>
   <si>
-    <t>Marshall Taylor</t>
-  </si>
-  <si>
     <t>Matt Kavney</t>
   </si>
   <si>
@@ -305,9 +284,6 @@
     <t>Ryan Mahlan</t>
   </si>
   <si>
-    <t>Sid Chitnis</t>
-  </si>
-  <si>
     <t>Susanna O'Brien</t>
   </si>
   <si>
@@ -344,9 +320,6 @@
     <t>Count</t>
   </si>
   <si>
-    <t>Specialty</t>
-  </si>
-  <si>
     <t>Abhinav Pal</t>
   </si>
   <si>
@@ -371,9 +344,6 @@
     <t>Adnan Sura</t>
   </si>
   <si>
-    <t>Adriana Stacey</t>
-  </si>
-  <si>
     <t>Afnan Ahmed</t>
   </si>
   <si>
@@ -389,9 +359,6 @@
     <t>Ajay Arelli</t>
   </si>
   <si>
-    <t>Akshat Jamad</t>
-  </si>
-  <si>
     <t>Alberico Altieri</t>
   </si>
   <si>
@@ -407,9 +374,6 @@
     <t>Alessandro Rossi</t>
   </si>
   <si>
-    <t>Alexander Garcia</t>
-  </si>
-  <si>
     <t>Alexandra Lac</t>
   </si>
   <si>
@@ -459,6 +423,63 @@
   </si>
   <si>
     <t>52</t>
+  </si>
+  <si>
+    <t>CVAS - IP Valuation</t>
+  </si>
+  <si>
+    <t>CSDN-0000002536</t>
+  </si>
+  <si>
+    <t>No Restrictions</t>
+  </si>
+  <si>
+    <t>TAS - ESG Due Diligence &amp; Analytics</t>
+  </si>
+  <si>
+    <t>Tombstone Permission</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>CF Financial User</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Liz Hedgcock</t>
+  </si>
+  <si>
+    <t>CAO</t>
+  </si>
+  <si>
+    <t>Opp Approver</t>
+  </si>
+  <si>
+    <t>Indrajeet Singh</t>
+  </si>
+  <si>
+    <t>System Admin</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Opportunities</t>
+  </si>
+  <si>
+    <t>Engagements</t>
   </si>
 </sst>
 </file>
@@ -490,7 +511,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -498,30 +519,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -530,6 +535,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -549,9 +560,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -589,7 +600,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -695,7 +706,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -837,196 +848,31 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
-  <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="U2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V2" t="s">
-        <v>44</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1034,25 +880,78 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="76.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{412C6B22-BBF2-46A2-ADA2-F9697D971635}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>136</v>
+      </c>
+      <c r="C2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1061,60 +960,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E00E11C-92FC-42B5-B038-F40502DA172C}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1123,317 +980,26 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
-  <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA334E8-544E-4404-B277-D7EB85658B48}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1442,42 +1008,322 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
+  <dimension ref="A1:AE3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="H2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3">
+      <c r="O2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC2" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD2" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE2" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>65</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC3" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE3" s="7">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1486,26 +1332,60 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>125</v>
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1514,40 +1394,380 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="76.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>138</v>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/TestData/TMTT0035667_VerifyInternalDealTeamForAnalystRoleLimitForFVALOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035667_VerifyInternalDealTeamForAnalystRoleLimitForFVALOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B04F765-3300-4DB3-8110-E75D331EFFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6912768-A6C0-4E91-8E80-DBA86E140761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>

--- a/TestData/TMTT0035667_VerifyInternalDealTeamForAnalystRoleLimitForFVALOBOpportunityEngagement.xlsx
+++ b/TestData/TMTT0035667_VerifyInternalDealTeamForAnalystRoleLimitForFVALOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF83111-D205-4A13-B30C-F6CBEDF6E022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4460EF42-2BA1-4B1B-A04F-DFAC15F266AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -449,9 +449,6 @@
     <t>Group</t>
   </si>
   <si>
-    <t>Liz Hedgcock</t>
-  </si>
-  <si>
     <t>CAO</t>
   </si>
   <si>
@@ -480,6 +477,9 @@
   </si>
   <si>
     <t>BUS - Business Services</t>
+  </si>
+  <si>
+    <t>Blaise Brunda</t>
   </si>
 </sst>
 </file>
@@ -923,6 +923,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{412C6B22-BBF2-46A2-ADA2-F9697D971635}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -937,21 +940,21 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" t="s">
         <v>134</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>135</v>
-      </c>
-      <c r="C2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" t="s">
         <v>137</v>
-      </c>
-      <c r="B3" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -966,12 +969,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -989,17 +992,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1147,7 +1150,7 @@
         <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>30</v>
@@ -1242,7 +1245,7 @@
         <v>128</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>30</v>
